--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_191_Croatia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_191_Croatia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R0a8227cc9fb54fe5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R95cd84eb70864c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd0786170ac704604"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf7d952403827402e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Reb39ace56000489e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8127f4e79598404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R8237fb157d0f4427"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb85bd52650eb46d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1a0f50da72494f1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R2e18ec7e46d943a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R549eded1bbc24ad4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R786ef27533fb415e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ191CommercialTable" displayName="EEZ191CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ191CommercialTable" displayName="EEZ191CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ191FunctionalTable" displayName="EEZ191FunctionalTable" ref="A1:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O17"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ191FunctionalTable" displayName="EEZ191FunctionalTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E17"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ191ValidationTable" displayName="EEZ191ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ191ValidationTable" displayName="EEZ191ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3709,7 +3663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R902ac844fcc9414c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R060dfef9ff134447"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3719,20 +3673,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3740,606 +3684,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>10154.0682814682</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.118849156848166</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>131.476809553651</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>10154.0682814682</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>131.74167306394332</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$46,A2,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1337713.9438061405</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.118849156848166</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>131.476809553651</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1335024.5016373629</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2689.4421687775757</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0020145264491245</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0020145264491243904</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1783.6560895068</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.261095376978488</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1824.2962986236357</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1783.6560895068</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2063.9950174909727</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$46,A3,'Species'!$U$2:$U$46))</x:f>
-        <x:v>3681457.281659468</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.261095376978488</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1824.2962986236357</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3253917.2021047636</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>427540.0795547045</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.131392427342083</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.1313924273420831</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>483.6534921858001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.8975407676048075</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>78.98429891757985</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>483.6534921858001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>81.77335388387966</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$46,A4,'Species'!$U$2:$U$46))</x:f>
-        <x:v>39549.96817368366</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.8975407676048075</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>78.98429891757985</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>38201.031999334606</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1348.9361743490517</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0353115113322737</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.035311511332273636</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>709.3718302606</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.1499999999999995</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>141.25375446227525</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>709.3718302606</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$46,A5,'Species'!$U$2:$U$46))</x:f>
-        <x:v>100201.43433408569</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.1499999999999995</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>141.25375446227525</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>100201.43433408558</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1.0186340659856796e-10</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.0165863121174605e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>48353.411555478306</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0603869905112795</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>114.91771725627959</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>48353.411555478306</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>114.93329487298627</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$46,A6,'Species'!$U$2:$U$46))</x:f>
-        <x:v>5557416.908420649</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0603869905112795</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>114.91771725627959</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5556663.677508978</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>753.230911671184</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0001355545261306</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00013555452613048073</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>9185.236562752098</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.376480866171637</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>237.94734655469566</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>9185.236562752098</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>277.7374900928293</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$46,A7,'Species'!$U$2:$U$46))</x:f>
-        <x:v>2551084.5488476544</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.376480866171637</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>237.94734655469566</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2185602.667584035</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>365481.8812636193</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1672224721740585</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.16722247217405847</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4079.9934932567007</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.475377853896406</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>298.798115370001</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4079.9934932567007</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>421.38973409738884</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$46,A8,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1719267.3732425177</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.475377853896406</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>298.798115370001</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1219094.366506969</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>500173.0067355486</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.410282436271671</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.41028243627167094</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>84.85119619400001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.139247720123708</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1377.9952486625252</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>84.85119619400001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1460.616485945727</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$46,A9,'Species'!$U$2:$U$46))</x:f>
-        <x:v>123935.05601317174</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.139247720123708</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1377.9952486625252</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>116924.54519866376</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>7010.510814507972</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0599575632524085</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.05995756325240844</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.36677227149999997</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.440404012815347</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2756.792082514434</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.36677227149999997</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>3034.520370421456</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$46,A10,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1112.9779291724988</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.440404012815347</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2756.792082514434</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1011.1148941570342</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>101.86303501546456</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1007432840759286</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.10074328407592859</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2238.3641143326995</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.4239359082894385</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2654.213833172092</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2238.3641143326995</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2680.091539797133</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$46,A11,'Species'!$U$2:$U$46))</x:f>
-        <x:v>5999020.72580857</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.4239359082894385</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2654.213833172092</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>5941096.995937849</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>57923.72987072077</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0097496691116683</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.009749669111668332</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R454cd75e46eb4a6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R084e51b9f1904ed4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4349,20 +3899,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4370,930 +3910,326 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1758.0752609207</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8100000000000005</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>645.6542290346563</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1758.0752609207</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>645.6542290346556</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$46,A2,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1135108.7271746555</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8100000000000005</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>645.6542290346563</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1135108.7271746567</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>-1.1641532182693481e-9</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>-1.0255874088528811e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>212.4615969882</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.82</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>660.6934480075957</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>212.4615969882</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$46,A3,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>140371.9850833341</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.82</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>140371.9850833341</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1227.9086414615</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.42</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2630.2679918953813</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1227.9086414615</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$46,A4,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3229728.7966079256</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.42</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>3229728.7966079256</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2114.7388081951</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.419999053986279</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2630.2622624491114</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2114.7388081951</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2654.4017704628477</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$46,A5,'Species'!$U$2:$U$46))</x:f>
-        <x:v>5613366.436539565</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.419999053986279</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2630.2622624491114</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>5562317.682132181</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>51048.75440738443</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0091776049705625</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.00917760497056258</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.0212331963</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.38</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>239.88329190194898</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.0212331963</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$46,A6,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5.093489026044283</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.38</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>5.093489026044283</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>69.4362968605</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.262130835718404</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1828.651033264601</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>69.4362968605</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2206.489054756804</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$46,A7,'Species'!$U$2:$U$46))</x:f>
-        <x:v>153210.42902553745</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.262130835718404</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1828.651033264601</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>126974.75600002088</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>26235.673025516575</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.206621172995302</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.206621172995302</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.3455390752</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.505565287407472</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>3203.0615740794733</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.3455390752</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>3206.2493641426936</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$46,A8,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1107.8844401464544</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.505565287407472</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>3203.0615740794733</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1106.7829341160775</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1.1015060303768678</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0009952322143967</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0009952322143967425</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>483.6534921858001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.8975407676048075</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>78.98429891757985</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>483.6534921858001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>81.77335388387966</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$46,A9,'Species'!$U$2:$U$46))</x:f>
-        <x:v>39549.96817368366</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.8975407676048075</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>78.98429891757985</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>38201.031999334606</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1348.9361743490517</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0353115113322737</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.035311511332273636</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>732.1437339249</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.765441265664624</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>582.6949653311314</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>732.1437339249</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>666.1861072753348</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$46,A10,'Species'!$U$2:$U$46))</x:f>
-        <x:v>487743.9840694576</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.765441265664624</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>582.6949653311314</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>426616.4676567746</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>61127.516412683006</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1432844745736863</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.14328447457368634</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>8239.807327640701</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.26838433011578</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>185.51726374091487</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>8239.807327640701</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>195.2414132404119</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$46,A11,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1608751.6274772722</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.26838433011578</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>185.51726374091487</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1528626.5091762429</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>80125.11830102932</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0524164129171145</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.05241641291711453</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1950.865817476</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.762064796079108</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>578.1823048952438</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1950.865817476</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>739.8166724103279</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$46,A12,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1443283.0574041484</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.762064796079108</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>578.1823048952438</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1127956.0948896175</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>315326.96251453087</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2795560606863772</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.2795560606863771</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>703.7624954607</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.1428701196765507</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>138.95370134396725</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>703.7624954607</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>201.61229453299674</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$46,A13,'Species'!$U$2:$U$46))</x:f>
-        <x:v>141887.17151609945</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.1428701196765507</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>138.95370134396725</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>97790.40361133122</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>44096.76790476823</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.4509314439485412</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.4509314439485413</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$46,A14,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>450</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>317.901477114</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.58</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>380.1893963205613</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>317.901477114</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$46,A15,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>120862.77067338639</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.58</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>120862.77067338639</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>58507.479836946506</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.070533194561115</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>117.63408928669291</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>58507.479836946506</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>117.85041624494357</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$46,A16,'Species'!$U$2:$U$46))</x:f>
-        <x:v>6895130.852226789</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.070533194561115</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>117.63408928669291</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>6882474.107078751</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>12656.745148038492</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0018389818764477</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.001838981876447715</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>709.3718302606</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1499999999999995</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>141.25375446227525</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>709.3718302606</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$46,A17,'Species'!$U$2:$U$46))</x:f>
-        <x:v>100201.43433408569</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1499999999999995</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>141.25375446227525</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>100201.43433408558</x:v>
       </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>1.0186340659856796e-10</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.0165863121174605e-15</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G17">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O17">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50ec41cf79ef46df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c1c412446f04b86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5468,7 +4404,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5567,7 +4503,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>21110760.218235113</x:v>
+        <x:v>19747737.5377062</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5581,7 +4517,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>21110760.218235113</x:v>
+        <x:v>20518792.64284078</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5595,7 +4531,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1363022.6805289127</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5609,7 +4545,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-591967.5753943324</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5620,9 +4556,9 @@
         <x:v>EEZ_191</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5634,47 +4570,19 @@
         <x:v>EEZ_191</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_191</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_191</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33bc47444f0c4844"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d3fb73612274081"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5721,7 +4629,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
